--- a/accountant-skill/data/Jan2026/trial_balance_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/trial_balance_Jan2026.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjustments" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjusted TB" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB Worksheet" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +65,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="11"/>
@@ -73,13 +85,8 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +101,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -144,17 +156,20 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,11 +536,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -597,15 +612,17 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>21693000</v>
+        <v>20138000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>21518000</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>-1380000</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -616,15 +633,17 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>21762750</v>
+        <v>20207750</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>21762750</v>
-      </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>21587750</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>-1380000</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -655,7 +674,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -665,7 +684,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -675,7 +694,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15"/>
@@ -720,15 +739,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>21693000</v>
+        <v>20138000</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>21518000</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>-1380000</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -739,15 +760,17 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>21762750</v>
+        <v>20207750</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>21762750</v>
-      </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>21587750</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>-1380000</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -764,20 +787,53 @@
         <v>87750</v>
       </c>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>WARNINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Unadjusted TB NOT balanced: Dr 20,138,000.00 vs Cr 21,518,000.00 (diff -1,380,000.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Adjusted TB NOT balanced: Dr 20,207,750.00 vs Cr 21,587,750.00 (diff -1,380,000.00)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -790,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -859,11 +915,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>1020</v>
+        <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
+          <t>Cash in hand</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -877,17 +933,17 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1438500</v>
+        <v>150000</v>
       </c>
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>1030</v>
+        <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Petty Cash</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -901,13 +957,13 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>150000</v>
+        <v>1438500</v>
       </c>
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -925,17 +981,17 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3360000</v>
+        <v>2605000</v>
       </c>
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>1110</v>
+        <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Allowance for Doubtful Debts</t>
+          <t>Inventory - Raw Material</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -945,21 +1001,21 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n">
-        <v>15000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>1200</v>
+        <v>13000</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Inventory — Raw Materials</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -973,17 +1029,17 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>1320</v>
+        <v>15100</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -997,17 +1053,17 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>1610</v>
+        <v>15110</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1017,21 +1073,21 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n">
+        <v>500000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>1611</v>
+        <v>15200</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Buildings</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1041,21 +1097,21 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n">
-        <v>500000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>1620</v>
+        <v>15210</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1065,21 +1121,21 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F14" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n">
+        <v>450000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>1621</v>
+        <v>15300</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Plant &amp; Machinery</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1089,21 +1145,21 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>450000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>1630</v>
+        <v>15310</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Furniture &amp; Fixtures</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1113,26 +1169,26 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>800000</v>
-      </c>
-      <c r="F16" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>1631</v>
+        <v>20000</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Account 1631</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1142,45 +1198,45 @@
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n">
-        <v>160000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>1650</v>
+        <v>21000</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>1651</v>
+        <v>22200</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Office Equipment</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1190,16 +1246,16 @@
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n">
-        <v>100000</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>2010</v>
+        <v>25000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1214,45 +1270,45 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>1368000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>2030</v>
+        <v>30200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages &amp; Salaries</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n">
-        <v>205000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>2060</v>
+        <v>31000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1262,21 +1318,21 @@
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
-        <v>500000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>2100</v>
+        <v>32000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Long-term Loans</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1286,21 +1342,21 @@
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>3010</v>
+        <v>40000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1310,21 +1366,21 @@
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n">
-        <v>7680000</v>
+        <v>7515000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>3020</v>
+        <v>50000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Owner's Drawings</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1333,159 +1389,161 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>200000</v>
+        <v>2096000</v>
       </c>
       <c r="F25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>3030</v>
+        <v>50100</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>4010</v>
+        <v>60000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 1</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n">
-        <v>1710000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>4020</v>
+        <v>61000</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 2</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n">
-        <v>2090000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>4030</v>
+        <v>62000</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 3</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n">
-        <v>1310000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>4040</v>
+        <v>63000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — General</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n">
-        <v>2405000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>4110</v>
+        <v>64000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n"/>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>85000</v>
+      </c>
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>5010</v>
+        <v>65000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Raw Materials Used</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1499,17 +1557,17 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>2096000</v>
+        <v>1468500</v>
       </c>
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>5020</v>
+        <v>66000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Packaging Costs</t>
+          <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1522,328 +1580,62 @@
           <t>Debit</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n">
-        <v>225000</v>
-      </c>
+      <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>5100</v>
+        <v>70000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>2755000</v>
-      </c>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>5110</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Rent Expense</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="F36" s="7" t="n"/>
-    </row>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n">
+        <v>20138000</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>21518000</v>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>5210</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Utilities Expense</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="F37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>55000</v>
-      </c>
-      <c r="F38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>5300</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>5420</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; Sanitation</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Delivery</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Advertising</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
-        <v>5920</v>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>21693000</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>Dr 21,693,000.00 = Cr 21,693,000.00</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Dr 20,138,000.00 = Cr 21,518,000.00</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1864,17 +1656,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1988,7 +1780,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -1996,12 +1788,12 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Buildings</t>
+          <t>Accum. Depr. — Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="J7" s="7" t="n">
@@ -2036,7 +1828,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -2044,12 +1836,12 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Plant &amp; Machinery</t>
+          <t>Accum. Depr. — Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="J8" s="7" t="n">
@@ -2084,24 +1876,24 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Furniture &amp; Fixtures</t>
+          <t>Accum. Depr. — Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="10">
@@ -2117,39 +1909,39 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Bank Recon</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Depreciation — Office Equipment</t>
+          <t>Bank Interest Earned</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Office Equipment</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="11">
@@ -2170,152 +1962,128 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Bank Interest Earned</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
+          <t>Telephone &amp; Internet</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>65000</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
           <t>Cash at Bank</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n">
+        <v>87750</v>
+      </c>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n">
+        <v>87750</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PER-ACCOUNT ADJUSTMENT SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Account Code</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Total Dr Adj</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Total Cr Adj</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Net Effect on Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>10100</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Cash at Bank</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>4110</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>ADJ-006</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Bank Recon</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Software / Subscription</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>18000</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Cash at Bank</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n">
-        <v>87750</v>
-      </c>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n">
-        <v>87750</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>PER-ACCOUNT ADJUSTMENT SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Account Code</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Total Dr Adj</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Total Cr Adj</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Net Effect on Balance</t>
-        </is>
+      <c r="F17" s="8" t="n">
+        <v>-3000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>1020</v>
+        <v>15110</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -2323,23 +2091,21 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>15000</v>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>-3000</v>
+        <v>18750</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>18750</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>1611</v>
+        <v>15210</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Buildings</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -2349,19 +2115,19 @@
       </c>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>18750</v>
+        <v>22500</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18750</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>1621</v>
+        <v>15310</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Plant &amp; Machinery</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -2371,59 +2137,59 @@
       </c>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22500</v>
+        <v>13500</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>22500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>1631</v>
+        <v>65000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Account 1631</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n">
-        <v>6000</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>1651</v>
+        <v>66000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Office Equipment</t>
+          <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n">
-        <v>7500</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
-        <v>7500</v>
+        <v>54750</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>4110</v>
+        <v>70000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
@@ -2443,57 +2209,13 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>5300</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n">
-        <v>54750</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2506,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2575,11 +2297,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>1020</v>
+        <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
+          <t>Cash in hand</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -2593,17 +2315,17 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1435500</v>
+        <v>150000</v>
       </c>
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>1030</v>
+        <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Petty Cash</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2617,13 +2339,13 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>150000</v>
+        <v>1435500</v>
       </c>
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -2641,17 +2363,17 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3360000</v>
+        <v>2605000</v>
       </c>
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>1110</v>
+        <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Allowance for Doubtful Debts</t>
+          <t>Inventory - Raw Material</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2661,21 +2383,21 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n">
-        <v>15000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>1200</v>
+        <v>13000</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Inventory — Raw Materials</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2689,17 +2411,17 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>1320</v>
+        <v>15100</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2713,17 +2435,17 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>1610</v>
+        <v>15110</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -2733,21 +2455,21 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n">
+        <v>518750</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>1611</v>
+        <v>15200</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Buildings</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -2757,21 +2479,21 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n">
-        <v>518750</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>1620</v>
+        <v>15210</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -2781,21 +2503,21 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F14" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n">
+        <v>472500</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>1621</v>
+        <v>15300</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Plant &amp; Machinery</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -2805,21 +2527,21 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>472500</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>1630</v>
+        <v>15310</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Furniture &amp; Fixtures</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -2829,26 +2551,26 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>800000</v>
-      </c>
-      <c r="F16" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n">
+        <v>113500</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>1631</v>
+        <v>20000</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Account 1631</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2858,45 +2580,45 @@
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n">
-        <v>166000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>1650</v>
+        <v>21000</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>1651</v>
+        <v>22200</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Office Equipment</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2906,16 +2628,16 @@
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n">
-        <v>107500</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>2010</v>
+        <v>25000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -2930,45 +2652,45 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>1368000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>2030</v>
+        <v>30200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages &amp; Salaries</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n">
-        <v>205000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>2060</v>
+        <v>31000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -2978,21 +2700,21 @@
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
-        <v>500000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>2100</v>
+        <v>32000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Long-term Loans</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -3002,21 +2724,21 @@
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>3010</v>
+        <v>40000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -3026,21 +2748,21 @@
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n">
-        <v>7680000</v>
+        <v>7515000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>3020</v>
+        <v>50000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Owner's Drawings</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -3049,161 +2771,161 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>200000</v>
+        <v>2096000</v>
       </c>
       <c r="F25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>3030</v>
+        <v>50100</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>4010</v>
+        <v>60000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 1</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n">
-        <v>1710000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>4020</v>
+        <v>61000</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 2</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n">
-        <v>2090000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>4030</v>
+        <v>62000</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 3</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n">
-        <v>1310000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>4040</v>
+        <v>63000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — General</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n">
-        <v>2405000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>4110</v>
+        <v>64000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n">
-        <v>15000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>5010</v>
+        <v>65000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Raw Materials Used</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -3217,17 +2939,17 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>2096000</v>
+        <v>1486500</v>
       </c>
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>5020</v>
+        <v>66000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Packaging Costs</t>
+          <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -3241,329 +2963,65 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>225000</v>
+        <v>54750</v>
       </c>
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>5100</v>
+        <v>70000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="F34" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n">
+        <v>15000</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>5110</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Rent Expense</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="F36" s="7" t="n"/>
-    </row>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n">
+        <v>20207750</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>21587750</v>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>5210</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Utilities Expense</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="F37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>73000</v>
-      </c>
-      <c r="F38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>5300</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="F39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>5420</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; Sanitation</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Delivery</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Advertising</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
-        <v>5920</v>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n">
-        <v>21762750</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>21762750</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>Dr 21,762,750.00 = Cr 21,762,750.00</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Dr 20,207,750.00 = Cr 21,587,750.00</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -3669,11 +3127,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>1020</v>
+        <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
+          <t>Cash in hand</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -3682,27 +3140,23 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1438500</v>
+        <v>150000</v>
       </c>
       <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>18000</v>
-      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n">
-        <v>1435500</v>
+        <v>150000</v>
       </c>
       <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>1030</v>
+        <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Petty Cash</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -3711,19 +3165,23 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>150000</v>
+        <v>1438500</v>
       </c>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="F7" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>18000</v>
+      </c>
       <c r="H7" s="7" t="n">
-        <v>150000</v>
+        <v>1435500</v>
       </c>
       <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -3736,23 +3194,23 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3360000</v>
+        <v>2605000</v>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n">
-        <v>3360000</v>
+        <v>2605000</v>
       </c>
       <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>1110</v>
+        <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Allowance for Doubtful Debts</t>
+          <t>Inventory - Raw Material</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3760,24 +3218,24 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n">
-        <v>15000</v>
-      </c>
+      <c r="D9" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n">
-        <v>15000</v>
-      </c>
+      <c r="H9" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>1200</v>
+        <v>13000</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Inventory — Raw Materials</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3786,23 +3244,23 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>1320</v>
+        <v>15100</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3811,23 +3269,23 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="I11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>1610</v>
+        <v>15110</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3835,24 +3293,26 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n">
+        <v>500000</v>
+      </c>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I12" s="7" t="n"/>
+      <c r="G12" s="7" t="n">
+        <v>18750</v>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n">
+        <v>518750</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>1611</v>
+        <v>15200</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Buildings</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3860,26 +3320,24 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n">
-        <v>500000</v>
-      </c>
+      <c r="D13" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n">
-        <v>18750</v>
-      </c>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n">
-        <v>518750</v>
-      </c>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>1620</v>
+        <v>15210</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3887,24 +3345,26 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n">
+        <v>450000</v>
+      </c>
       <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="I14" s="7" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>22500</v>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n">
+        <v>472500</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>1621</v>
+        <v>15300</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Plant &amp; Machinery</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3912,26 +3372,24 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n">
-        <v>450000</v>
-      </c>
+      <c r="D15" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n">
-        <v>22500</v>
-      </c>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n">
-        <v>472500</v>
-      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>1630</v>
+        <v>15310</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Furniture &amp; Fixtures</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -3939,103 +3397,101 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>800000</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n">
+        <v>100000</v>
+      </c>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n">
-        <v>800000</v>
-      </c>
-      <c r="I16" s="7" t="n"/>
+      <c r="G16" s="7" t="n">
+        <v>13500</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n">
+        <v>113500</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>1631</v>
+        <v>20000</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Account 1631</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>160000</v>
+        <v>1368000</v>
       </c>
       <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n">
-        <v>6000</v>
-      </c>
+      <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n">
-        <v>166000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>1650</v>
+        <v>21000</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="I18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>1651</v>
+        <v>22200</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Office Equipment</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>100000</v>
+        <v>205000</v>
       </c>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n">
-        <v>7500</v>
-      </c>
+      <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n">
-        <v>107500</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>2010</v>
+        <v>25000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -4045,297 +3501,297 @@
       </c>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>1368000</v>
+        <v>2000000</v>
       </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n">
-        <v>1368000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>2030</v>
+        <v>30200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages &amp; Salaries</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n">
-        <v>205000</v>
-      </c>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n">
-        <v>205000</v>
-      </c>
+      <c r="H21" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>2060</v>
+        <v>31000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>500000</v>
+        <v>7680000</v>
       </c>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n">
-        <v>500000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>2100</v>
+        <v>32000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Long-term Loans</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>3010</v>
+        <v>40000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>7680000</v>
+        <v>7515000</v>
       </c>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n">
-        <v>7680000</v>
+        <v>7515000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>3020</v>
+        <v>50000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Owner's Drawings</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>200000</v>
+        <v>2096000</v>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n">
-        <v>200000</v>
+        <v>2096000</v>
       </c>
       <c r="I25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>3030</v>
+        <v>50100</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n">
-        <v>1200000</v>
-      </c>
+      <c r="H26" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="I26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>4010</v>
+        <v>60000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 1</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n">
-        <v>1710000</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n">
-        <v>1710000</v>
-      </c>
+      <c r="H27" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>4020</v>
+        <v>61000</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 2</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n">
-        <v>2090000</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n">
-        <v>2090000</v>
-      </c>
+      <c r="H28" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="I28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>4030</v>
+        <v>62000</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 3</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n">
-        <v>1310000</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n">
-        <v>1310000</v>
-      </c>
+      <c r="H29" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>4040</v>
+        <v>63000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — General</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n">
-        <v>2405000</v>
-      </c>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n">
-        <v>2405000</v>
-      </c>
+      <c r="H30" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>4110</v>
+        <v>64000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n"/>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>85000</v>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n">
-        <v>15000</v>
-      </c>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>5010</v>
+        <v>65000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Raw Materials Used</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -4344,23 +3800,25 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2096000</v>
+        <v>1468500</v>
       </c>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
+      <c r="F32" s="7" t="n">
+        <v>18000</v>
+      </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n">
-        <v>2096000</v>
+        <v>1486500</v>
       </c>
       <c r="I32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>5020</v>
+        <v>66000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Packaging Costs</t>
+          <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -4368,366 +3826,89 @@
           <t>Expense</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
-        <v>225000</v>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
+      <c r="F33" s="7" t="n">
+        <v>54750</v>
+      </c>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n">
-        <v>225000</v>
+        <v>54750</v>
       </c>
       <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>5100</v>
+        <v>70000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>2755000</v>
-      </c>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="I34" s="7" t="n"/>
+      <c r="G34" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n">
+        <v>15000</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>5110</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Rent Expense</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="I36" s="7" t="n"/>
-    </row>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n">
+        <v>20138000</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>21518000</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>87750</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>87750</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>20207750</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>21587750</v>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>5210</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Utilities Expense</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="I37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n">
-        <v>73000</v>
-      </c>
-      <c r="I38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>5300</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="I39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n">
-        <v>95000</v>
-      </c>
-      <c r="I40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>5420</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; Sanitation</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="I41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Delivery</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Advertising</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
-        <v>5920</v>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="I45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>87750</v>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>87750</v>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>21762750</v>
-      </c>
-      <c r="I46" s="10" t="n">
-        <v>21762750</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Unadj. Dr=Cr</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Adjusted Dr=Cr</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -4739,4 +3920,72 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exceptions &amp; Warnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Exception / Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Unadjusted TB NOT balanced: Dr 20,138,000.00 vs Cr 21,518,000.00 (diff -1,380,000.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Adjusted TB NOT balanced: Dr 20,207,750.00 vs Cr 21,587,750.00 (diff -1,380,000.00)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/accountant-skill/data/Jan2026/trial_balance_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/trial_balance_Jan2026.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>20138000</v>
+        <v>20463000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>21518000</v>
+        <v>21583000</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>-1380000</v>
+        <v>-1120000</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>20207750</v>
+        <v>20532750</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>21587750</v>
+        <v>21652750</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>-1380000</v>
+        <v>-1120000</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>20138000</v>
+        <v>20463000</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>21518000</v>
+        <v>21583000</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>-1380000</v>
+        <v>-1120000</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>20207750</v>
+        <v>20532750</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>21587750</v>
+        <v>21652750</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>-1380000</v>
+        <v>-1120000</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Unadjusted TB NOT balanced: Dr 20,138,000.00 vs Cr 21,518,000.00 (diff -1,380,000.00)</t>
+          <t>Unadjusted TB NOT balanced: Dr 20,463,000.00 vs Cr 21,583,000.00 (diff -1,120,000.00)</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Adjusted TB NOT balanced: Dr 20,207,750.00 vs Cr 21,587,750.00 (diff -1,380,000.00)</t>
+          <t>Adjusted TB NOT balanced: Dr 20,532,750.00 vs Cr 21,652,750.00 (diff -1,120,000.00)</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1011,11 +1011,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>13000</v>
+        <v>12200</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Inventory - Finished Goods</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1029,17 +1029,17 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>100000</v>
+        <v>260000</v>
       </c>
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>15100</v>
+        <v>12400</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Buildings &amp; Structures</t>
+          <t>Work-in-Progress</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1053,17 +1053,17 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>5000000</v>
+        <v>65000</v>
       </c>
       <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>15110</v>
+        <v>13000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1073,21 +1073,21 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n">
-        <v>500000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Machinery &amp; Equipment</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1101,17 +1101,17 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>15210</v>
+        <v>15110</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1126,16 +1126,16 @@
       </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Office &amp; Facility Equipment</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1149,17 +1149,17 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>15310</v>
+        <v>15210</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1174,45 +1174,45 @@
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n">
-        <v>100000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>20000</v>
+        <v>15300</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n">
-        <v>1368000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>21000</v>
+        <v>15310</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1222,16 +1222,16 @@
       </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>22200</v>
+        <v>20000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n">
-        <v>205000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>25000</v>
+        <v>21000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1270,45 +1270,45 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>30200</v>
+        <v>22200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Account 30200</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F21" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n">
+        <v>205000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Paid-up Capital</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1318,16 +1318,16 @@
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
-        <v>7680000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>32000</v>
+        <v>30200</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1337,26 +1337,26 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>40000</v>
+        <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1366,64 +1366,64 @@
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n">
-        <v>7515000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>50000</v>
+        <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="F25" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n">
+        <v>1200000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>50100</v>
+        <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="F26" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n">
+        <v>7515000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1437,17 +1437,17 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>120000</v>
+        <v>2096000</v>
       </c>
       <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>61000</v>
+        <v>50100</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1461,17 +1461,17 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>62000</v>
+        <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Meal Allowance Expense</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1484,18 +1484,18 @@
           <t>Debit</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n">
+        <v>65000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>63000</v>
+        <v>60000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Utilities (Electricity &amp; Water)</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1509,17 +1509,17 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>125000</v>
+        <v>120000</v>
       </c>
       <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>64000</v>
+        <v>61000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Transportation &amp; Distribution Expense</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1533,17 +1533,17 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>85000</v>
+        <v>2755000</v>
       </c>
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>65000</v>
+        <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1557,17 +1557,17 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1468500</v>
+        <v>120000</v>
       </c>
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>66000</v>
+        <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - SG&amp;A</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1580,60 +1580,132 @@
           <t>Debit</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n"/>
+      <c r="E33" s="7" t="n">
+        <v>125000</v>
+      </c>
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>1468500</v>
+      </c>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n">
-        <v>20138000</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>21518000</v>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n">
+        <v>20463000</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>21583000</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>Dr 20,138,000.00 = Cr 21,518,000.00</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Dr 20,463,000.00 = Cr 21,583,000.00</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2228,7 +2300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2393,11 +2465,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>13000</v>
+        <v>12200</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Inventory - Finished Goods</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2411,17 +2483,17 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>100000</v>
+        <v>260000</v>
       </c>
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>15100</v>
+        <v>12400</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Buildings &amp; Structures</t>
+          <t>Work-in-Progress</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2435,17 +2507,17 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>5000000</v>
+        <v>65000</v>
       </c>
       <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>15110</v>
+        <v>13000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -2455,21 +2527,21 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n">
-        <v>518750</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Machinery &amp; Equipment</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -2483,17 +2555,17 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>15210</v>
+        <v>15110</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -2508,16 +2580,16 @@
       </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n">
-        <v>472500</v>
+        <v>518750</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Office &amp; Facility Equipment</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -2531,17 +2603,17 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>15310</v>
+        <v>15210</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -2556,45 +2628,45 @@
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n">
-        <v>113500</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>20000</v>
+        <v>15300</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n">
-        <v>1368000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>21000</v>
+        <v>15310</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2604,16 +2676,16 @@
       </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>500000</v>
+        <v>113500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>22200</v>
+        <v>20000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -2628,16 +2700,16 @@
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n">
-        <v>205000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>25000</v>
+        <v>21000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -2652,45 +2724,45 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>30200</v>
+        <v>22200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Account 30200</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F21" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n">
+        <v>205000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Paid-up Capital</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -2700,16 +2772,16 @@
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
-        <v>7680000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>32000</v>
+        <v>30200</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2719,26 +2791,26 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>40000</v>
+        <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -2748,64 +2820,64 @@
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n">
-        <v>7515000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>50000</v>
+        <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="F25" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n">
+        <v>1200000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>50100</v>
+        <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="F26" s="7" t="n"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n">
+        <v>7515000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2819,17 +2891,17 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>120000</v>
+        <v>2096000</v>
       </c>
       <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>61000</v>
+        <v>50100</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -2843,17 +2915,17 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>62000</v>
+        <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Meal Allowance Expense</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -2866,18 +2938,18 @@
           <t>Debit</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n">
+        <v>65000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>63000</v>
+        <v>60000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Utilities (Electricity &amp; Water)</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2891,17 +2963,17 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>125000</v>
+        <v>120000</v>
       </c>
       <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>64000</v>
+        <v>61000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Transportation &amp; Distribution Expense</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2915,17 +2987,17 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>85000</v>
+        <v>2755000</v>
       </c>
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>65000</v>
+        <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2939,17 +3011,17 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1486500</v>
+        <v>120000</v>
       </c>
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>66000</v>
+        <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - SG&amp;A</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2963,63 +3035,135 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>54750</v>
+        <v>125000</v>
       </c>
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>1486500</v>
+      </c>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n">
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n">
-        <v>20207750</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>21587750</v>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n">
+        <v>20532750</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>21652750</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>Dr 20,207,750.00 = Cr 21,587,750.00</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Dr 20,532,750.00 = Cr 21,652,750.00</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3042,7 +3186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -3231,11 +3375,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>13000</v>
+        <v>12200</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Inventory - Finished Goods</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3244,23 +3388,23 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>100000</v>
+        <v>260000</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n">
-        <v>100000</v>
+        <v>260000</v>
       </c>
       <c r="I10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>15100</v>
+        <v>12400</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Buildings &amp; Structures</t>
+          <t>Work-in-Progress</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3269,23 +3413,23 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5000000</v>
+        <v>65000</v>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n">
-        <v>5000000</v>
+        <v>65000</v>
       </c>
       <c r="I11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>15110</v>
+        <v>13000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3293,26 +3437,24 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n">
-        <v>500000</v>
-      </c>
+      <c r="D12" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n">
-        <v>18750</v>
-      </c>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n">
-        <v>518750</v>
-      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Machinery &amp; Equipment</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3321,23 +3463,23 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>15210</v>
+        <v>15110</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3347,24 +3489,24 @@
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n">
-        <v>22500</v>
+        <v>18750</v>
       </c>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n">
-        <v>472500</v>
+        <v>518750</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Office &amp; Facility Equipment</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3373,23 +3515,23 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="I15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>15310</v>
+        <v>15210</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -3399,74 +3541,76 @@
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>100000</v>
+        <v>450000</v>
       </c>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n">
-        <v>13500</v>
+        <v>22500</v>
       </c>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n">
-        <v>113500</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>20000</v>
+        <v>15300</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n">
-        <v>1368000</v>
-      </c>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n">
-        <v>1368000</v>
-      </c>
+      <c r="H17" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>21000</v>
+        <v>15310</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
+      <c r="G18" s="7" t="n">
+        <v>13500</v>
+      </c>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n">
-        <v>500000</v>
+        <v>113500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>22200</v>
+        <v>20000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3476,22 +3620,22 @@
       </c>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>205000</v>
+        <v>1368000</v>
       </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n">
-        <v>205000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>25000</v>
+        <v>21000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -3501,72 +3645,72 @@
       </c>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>30200</v>
+        <v>22200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Account 30200</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E21" s="7" t="n"/>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n">
+        <v>205000</v>
+      </c>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n">
+        <v>205000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Paid-up Capital</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>7680000</v>
+        <v>2000000</v>
       </c>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n">
-        <v>7680000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>32000</v>
+        <v>30200</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3574,99 +3718,99 @@
           <t>Equity</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n">
-        <v>1200000</v>
-      </c>
+      <c r="D23" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n">
-        <v>1200000</v>
-      </c>
+      <c r="H23" s="7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>40000</v>
+        <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>7515000</v>
+        <v>7680000</v>
       </c>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n">
-        <v>7515000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>50000</v>
+        <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="E25" s="7" t="n"/>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n">
+        <v>1200000</v>
+      </c>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="I25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n">
+        <v>1200000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>50100</v>
+        <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E26" s="7" t="n"/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n">
+        <v>7515000</v>
+      </c>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="I26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n">
+        <v>7515000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -3675,23 +3819,23 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>120000</v>
+        <v>2096000</v>
       </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n">
-        <v>120000</v>
+        <v>2096000</v>
       </c>
       <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>61000</v>
+        <v>50100</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -3700,23 +3844,23 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="I28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>62000</v>
+        <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Meal Allowance Expense</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -3724,24 +3868,24 @@
           <t>Expense</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n">
+        <v>65000</v>
+      </c>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n">
+        <v>65000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>63000</v>
+        <v>60000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Utilities (Electricity &amp; Water)</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -3750,23 +3894,23 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>125000</v>
+        <v>120000</v>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n">
-        <v>125000</v>
+        <v>120000</v>
       </c>
       <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>64000</v>
+        <v>61000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Transportation &amp; Distribution Expense</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -3775,23 +3919,23 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>85000</v>
+        <v>2755000</v>
       </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n">
-        <v>85000</v>
+        <v>2755000</v>
       </c>
       <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>65000</v>
+        <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -3800,25 +3944,23 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1468500</v>
+        <v>120000</v>
       </c>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n">
-        <v>18000</v>
-      </c>
+      <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n">
-        <v>1486500</v>
+        <v>120000</v>
       </c>
       <c r="I32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>66000</v>
+        <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - SG&amp;A</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -3826,87 +3968,164 @@
           <t>Expense</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="n">
+        <v>125000</v>
+      </c>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n">
-        <v>54750</v>
-      </c>
+      <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n">
-        <v>54750</v>
+        <v>125000</v>
       </c>
       <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>70000</v>
+        <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n"/>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>85000</v>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1468500</v>
+      </c>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n">
+        <v>1486500</v>
+      </c>
+      <c r="I35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="I36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n">
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n">
-        <v>20138000</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>21518000</v>
-      </c>
-      <c r="F35" s="12" t="n">
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n">
+        <v>20463000</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>21583000</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>87750</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>87750</v>
       </c>
-      <c r="H35" s="12" t="n">
-        <v>20207750</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>21587750</v>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="H38" s="12" t="n">
+        <v>20532750</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>21652750</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Unadj. Dr=Cr</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Adjusted Dr=Cr</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3968,7 +4187,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Unadjusted TB NOT balanced: Dr 20,138,000.00 vs Cr 21,518,000.00 (diff -1,380,000.00)</t>
+          <t>Unadjusted TB NOT balanced: Dr 20,463,000.00 vs Cr 21,583,000.00 (diff -1,120,000.00)</t>
         </is>
       </c>
     </row>
@@ -3978,7 +4197,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Adjusted TB NOT balanced: Dr 20,207,750.00 vs Cr 21,587,750.00 (diff -1,380,000.00)</t>
+          <t>Adjusted TB NOT balanced: Dr 20,532,750.00 vs Cr 21,652,750.00 (diff -1,120,000.00)</t>
         </is>
       </c>
     </row>
